--- a/data/dsc_planting.xlsx
+++ b/data/dsc_planting.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
   <si>
     <t>Date</t>
   </si>
@@ -40,6 +40,18 @@
     <t>Water Drawers</t>
   </si>
   <si>
+    <t>First-Aid</t>
+  </si>
+  <si>
+    <t>SHEQ</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
     <t>2025-07-01</t>
   </si>
   <si>
@@ -58,22 +70,64 @@
     <t>2025-07-06</t>
   </si>
   <si>
+    <t>2025-07-07</t>
+  </si>
+  <si>
     <t>2025-07-08</t>
   </si>
   <si>
-    <t>5612</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>2025-07-10</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>2025-07-12</t>
+  </si>
+  <si>
+    <t>2025-07-13</t>
+  </si>
+  <si>
+    <t>2025-07-14</t>
+  </si>
+  <si>
+    <t>2025-07-15</t>
+  </si>
+  <si>
+    <t>2025-07-16</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>2025-07-22</t>
+  </si>
+  <si>
+    <t>2025-07-23</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>2025-07-25</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -431,10 +485,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -459,133 +513,1131 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2">
+        <v>5854</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>4.5</v>
+      </c>
+      <c r="E2">
+        <v>84</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>5831</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>78</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>5831</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>5.8</v>
+      </c>
+      <c r="E4">
+        <v>108</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
         <v>5832</v>
       </c>
-      <c r="C2">
-        <v>90</v>
-      </c>
-      <c r="D2">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>5.8</v>
+      </c>
+      <c r="E5">
+        <v>122</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>5832</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>4.5</v>
+      </c>
+      <c r="E6">
+        <v>114</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>5832</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>2.2</v>
+      </c>
+      <c r="E7">
+        <v>60</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>5454</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>4.5</v>
+      </c>
+      <c r="E8">
+        <v>98</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>5454</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>1.5</v>
+      </c>
+      <c r="E9">
+        <v>69</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>5612</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>5.7</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>123</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>5612</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>108</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12">
+        <v>5612</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>2.3</v>
+      </c>
+      <c r="E12">
+        <v>14</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13">
+        <v>5492</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>4.1</v>
+      </c>
+      <c r="E13">
+        <v>122</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14">
+        <v>2106</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0.8</v>
+      </c>
+      <c r="E14">
+        <v>13</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15">
+        <v>2106</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>2.7</v>
+      </c>
+      <c r="E15">
+        <v>25</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16">
+        <v>5219</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>1.5</v>
+      </c>
+      <c r="E16">
+        <v>54</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17">
+        <v>5492</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
         <v>4</v>
       </c>
-      <c r="E2">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>5833</v>
-      </c>
-      <c r="C3">
-        <v>80</v>
-      </c>
-      <c r="D3">
-        <v>3.8</v>
-      </c>
-      <c r="E3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
+      <c r="E17">
+        <v>68</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18">
+        <v>5492</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <v>70</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19">
+        <v>2106</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>1.5</v>
+      </c>
+      <c r="E19">
+        <v>21</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20">
+        <v>5442</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>5.5</v>
+      </c>
+      <c r="E20">
+        <v>96</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21">
+        <v>2106</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>1.5</v>
+      </c>
+      <c r="E21">
+        <v>23</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22">
+        <v>5442</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>36</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23">
+        <v>5418</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0.7</v>
+      </c>
+      <c r="E23">
+        <v>16</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24">
+        <v>2106</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>1.4</v>
+      </c>
+      <c r="E24">
+        <v>17</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25">
+        <v>5442</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>3.4</v>
+      </c>
+      <c r="E25">
+        <v>50</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26">
+        <v>5418</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0.5</v>
+      </c>
+      <c r="E26">
+        <v>26</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>2106</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0.5</v>
+      </c>
+      <c r="E27">
+        <v>20</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>2106</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0.4</v>
+      </c>
+      <c r="E28">
+        <v>21</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>5442</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0.6</v>
+      </c>
+      <c r="E29">
+        <v>7</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>5418</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>1.2</v>
+      </c>
+      <c r="E30">
+        <v>23</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>5414</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+      <c r="E31">
+        <v>60</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32">
+        <v>5418</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0.8</v>
+      </c>
+      <c r="E32">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>5834</v>
-      </c>
-      <c r="C4">
-        <v>40</v>
-      </c>
-      <c r="D4">
-        <v>2.9</v>
-      </c>
-      <c r="E4">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>5835</v>
-      </c>
-      <c r="C5">
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33">
+        <v>5418</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>1.2</v>
+      </c>
+      <c r="E33">
+        <v>68</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34">
+        <v>5418</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34">
+        <v>44</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35">
+        <v>3314</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>1.5</v>
+      </c>
+      <c r="E35">
+        <v>26</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" t="s">
         <v>35</v>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>5836</v>
-      </c>
-      <c r="C6">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>1.8</v>
-      </c>
-      <c r="E6">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>5837</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>0.89</v>
-      </c>
-      <c r="E7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" t="s">
-        <v>19</v>
+      <c r="E36" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" t="s">
+        <v>37</v>
+      </c>
+      <c r="G36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H36" t="s">
+        <v>34</v>
+      </c>
+      <c r="I36" t="s">
+        <v>34</v>
+      </c>
+      <c r="J36" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/data/dsc_planting.xlsx
+++ b/data/dsc_planting.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -133,8 +138,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,6 +202,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -243,7 +256,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -275,9 +288,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -309,6 +323,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -484,11 +499,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -520,7 +535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -528,7 +543,7 @@
         <v>5854</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>4.5</v>
@@ -552,7 +567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -560,7 +575,7 @@
         <v>5831</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -584,7 +599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -592,7 +607,7 @@
         <v>5831</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>5.8</v>
@@ -616,7 +631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -648,7 +663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -680,7 +695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -691,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E7">
         <v>60</v>
@@ -712,7 +727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -744,7 +759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -776,7 +791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -808,7 +823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -840,7 +855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -851,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E12">
         <v>14</v>
@@ -872,7 +887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -883,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="E13">
         <v>122</v>
@@ -904,7 +919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -936,7 +951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -968,7 +983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1000,7 +1015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1032,7 +1047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1064,7 +1079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1096,7 +1111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1128,7 +1143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1160,7 +1175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1192,7 +1207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1224,7 +1239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1256,7 +1271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1288,7 +1303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1320,7 +1335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -1352,7 +1367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -1384,7 +1399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1416,7 +1431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -1448,7 +1463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -1480,7 +1495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>29</v>
       </c>
@@ -1512,7 +1527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>30</v>
       </c>
@@ -1544,7 +1559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>31</v>
       </c>
@@ -1576,7 +1591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -1608,7 +1623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>32</v>
       </c>
